--- a/artfynd/A 54306-2021 artfynd.xlsx
+++ b/artfynd/A 54306-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54306-2021 artfynd.xlsx
+++ b/artfynd/A 54306-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7144242</v>
+        <v>7144244</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,36 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Forna hässle, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442620.4584528906</v>
+        <v>442620</v>
       </c>
       <c r="R2" t="n">
-        <v>6262446.295867528</v>
+        <v>6262446</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,24 +746,9 @@
           <t>2014-01-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-01-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal lönn</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +775,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7144244</v>
+        <v>7144242</v>
       </c>
       <c r="B3" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,37 +786,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Forna hässle, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442620.4584528906</v>
+        <v>442620</v>
       </c>
       <c r="R3" t="n">
-        <v>6262446.295867528</v>
+        <v>6262446</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,19 +845,14 @@
           <t>2014-01-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-01-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal lönn</t>
         </is>
       </c>
       <c r="AD3" t="b">
